--- a/data/trans_orig/P19C01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19C01-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91211</t>
+          <t>91938</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128261</t>
+          <t>128897</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>122943</t>
+          <t>121995</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>161926</t>
+          <t>159403</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>225264</t>
+          <t>223956</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>280648</t>
+          <t>278838</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,45%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>349576</t>
+          <t>348940</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>386626</t>
+          <t>385899</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>376178</t>
+          <t>378701</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>415161</t>
+          <t>416109</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>735293</t>
+          <t>737103</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>790677</t>
+          <t>791985</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,96%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>189831</t>
+          <t>191647</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>241465</t>
+          <t>241109</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>235301</t>
+          <t>237997</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>290580</t>
+          <t>294580</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>442575</t>
+          <t>446828</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>516044</t>
+          <t>514448</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,7%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>480663</t>
+          <t>481019</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>532297</t>
+          <t>530481</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>513646</t>
+          <t>509646</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>568925</t>
+          <t>566229</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1010310</t>
+          <t>1011906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1083779</t>
+          <t>1079526</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,73%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134884</t>
+          <t>134895</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>177905</t>
+          <t>177069</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>142356</t>
+          <t>142409</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>183054</t>
+          <t>184831</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>286762</t>
+          <t>289238</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>349580</t>
+          <t>352484</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>367184</t>
+          <t>368020</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>410205</t>
+          <t>410194</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>401555</t>
+          <t>399778</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>442253</t>
+          <t>442200</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>780118</t>
+          <t>777214</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>842936</t>
+          <t>840460</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,4%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>224910</t>
+          <t>224382</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>275566</t>
+          <t>275620</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>265830</t>
+          <t>264735</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>320468</t>
+          <t>322481</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>502392</t>
+          <t>505008</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>575982</t>
+          <t>581424</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>38,14%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>435625</t>
+          <t>435571</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>486281</t>
+          <t>486809</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>492599</t>
+          <t>490586</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>547237</t>
+          <t>548332</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>948277</t>
+          <t>942835</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1021867</t>
+          <t>1019251</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>66,87%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>692031</t>
+          <t>687407</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>776288</t>
+          <t>777003</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>813224</t>
+          <t>813931</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>914498</t>
+          <t>907265</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1528215</t>
+          <t>1525596</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1660205</t>
+          <t>1658507</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,92%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1679957</t>
+          <t>1679242</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1764214</t>
+          <t>1768838</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1825508</t>
+          <t>1832741</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1926782</t>
+          <t>1926075</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3536047</t>
+          <t>3537745</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3668037</t>
+          <t>3670656</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,64%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2012 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>113616</t>
+          <t>113523</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154529</t>
+          <t>155044</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>180830</t>
+          <t>183074</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>229410</t>
+          <t>231671</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>307847</t>
+          <t>306717</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>371557</t>
+          <t>371181</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,89%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>451422</t>
+          <t>450907</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>492335</t>
+          <t>492428</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>406391</t>
+          <t>404130</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>454971</t>
+          <t>452727</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>870195</t>
+          <t>870571</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>933905</t>
+          <t>935035</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,3%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>228771</t>
+          <t>230562</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>287253</t>
+          <t>286305</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>270001</t>
+          <t>269948</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>330491</t>
+          <t>325016</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>518878</t>
+          <t>513574</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>598587</t>
+          <t>595118</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,7%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>579745</t>
+          <t>580693</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>638227</t>
+          <t>636436</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>568302</t>
+          <t>573777</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>628792</t>
+          <t>628845</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1167205</t>
+          <t>1170674</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1246914</t>
+          <t>1252218</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,92%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>178278</t>
+          <t>178775</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>228247</t>
+          <t>229198</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>195410</t>
+          <t>195855</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>247079</t>
+          <t>246031</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>387804</t>
+          <t>388977</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>458797</t>
+          <t>459174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,96%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>407786</t>
+          <t>406835</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>457755</t>
+          <t>457258</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>430420</t>
+          <t>431468</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>482089</t>
+          <t>481644</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>854735</t>
+          <t>854358</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>925728</t>
+          <t>924555</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,39%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>236740</t>
+          <t>235476</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>291057</t>
+          <t>293045</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>322382</t>
+          <t>321959</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>382263</t>
+          <t>385241</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>573347</t>
+          <t>574810</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>654745</t>
+          <t>654136</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>37,62%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>514619</t>
+          <t>512631</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>568936</t>
+          <t>570200</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>550938</t>
+          <t>547960</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>610819</t>
+          <t>611242</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1084132</t>
+          <t>1084741</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1165530</t>
+          <t>1164067</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>66,94%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>803968</t>
+          <t>809706</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>910699</t>
+          <t>913371</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1023560</t>
+          <t>1023692</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1132517</t>
+          <t>1131777</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1851991</t>
+          <t>1863103</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2006171</t>
+          <t>2017148</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,29%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2003960</t>
+          <t>2001288</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2110691</t>
+          <t>2104953</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2012778</t>
+          <t>2013518</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2121735</t>
+          <t>2121603</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4053782</t>
+          <t>4042805</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4207962</t>
+          <t>4196850</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>160637</t>
+          <t>163651</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>204278</t>
+          <t>205085</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>196503</t>
+          <t>194306</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>240977</t>
+          <t>241899</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>368809</t>
+          <t>373189</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>435504</t>
+          <t>436954</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,86%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>320715</t>
+          <t>319908</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>364356</t>
+          <t>361342</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>303386</t>
+          <t>302464</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>347860</t>
+          <t>350057</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>633852</t>
+          <t>632402</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>700547</t>
+          <t>696167</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,1%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>303452</t>
+          <t>303922</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>359651</t>
+          <t>360603</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>327463</t>
+          <t>327808</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>386317</t>
+          <t>388669</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>648500</t>
+          <t>644144</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>730050</t>
+          <t>727692</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,25%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>456695</t>
+          <t>455743</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>512894</t>
+          <t>512424</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>480056</t>
+          <t>477704</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>538910</t>
+          <t>538565</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952669</t>
+          <t>955027</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1034219</t>
+          <t>1038575</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,72%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>191449</t>
+          <t>190313</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>239769</t>
+          <t>239244</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>224196</t>
+          <t>224592</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>272703</t>
+          <t>272127</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>429784</t>
+          <t>428440</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>497459</t>
+          <t>495708</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>43,86%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310591</t>
+          <t>311116</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>358911</t>
+          <t>360047</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>307035</t>
+          <t>307611</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>355542</t>
+          <t>355146</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>632639</t>
+          <t>634390</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>700314</t>
+          <t>701658</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,09%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>327673</t>
+          <t>329651</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>384435</t>
+          <t>384758</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>389430</t>
+          <t>391104</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>453327</t>
+          <t>450248</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>731409</t>
+          <t>734008</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>816474</t>
+          <t>816655</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,51%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>388200</t>
+          <t>387877</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>444962</t>
+          <t>442984</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>423514</t>
+          <t>426593</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>487411</t>
+          <t>485737</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>833002</t>
+          <t>832821</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>918067</t>
+          <t>915468</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,5%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1037677</t>
+          <t>1032978</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1143813</t>
+          <t>1137089</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1191683</t>
+          <t>1193046</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1299392</t>
+          <t>1302499</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2254138</t>
+          <t>2258370</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2403527</t>
+          <t>2401253</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,41%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1520520</t>
+          <t>1527244</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1626656</t>
+          <t>1631355</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1567923</t>
+          <t>1564816</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1675632</t>
+          <t>1674269</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3128121</t>
+          <t>3130395</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3277510</t>
+          <t>3273278</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>59,17%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue una revisión o chequeo en 2023 (tasa de respuesta: 99,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>285397</t>
+          <t>285618</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>341364</t>
+          <t>339701</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>324482</t>
+          <t>324689</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>364191</t>
+          <t>364709</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>620947</t>
+          <t>619547</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>691943</t>
+          <t>690720</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,7%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>269940</t>
+          <t>271603</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>325907</t>
+          <t>325686</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>287341</t>
+          <t>286823</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>327050</t>
+          <t>326843</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>570893</t>
+          <t>572116</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>641889</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,94%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>283013</t>
+          <t>300437</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>707417</t>
+          <t>709114</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>552352</t>
+          <t>551884</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>604009</t>
+          <t>605751</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>723072</t>
+          <t>700911</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1287547</t>
+          <t>1289358</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,11%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>460003</t>
+          <t>458306</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>884407</t>
+          <t>866983</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>338316</t>
+          <t>336574</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>389973</t>
+          <t>390441</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>822198</t>
+          <t>820387</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1386673</t>
+          <t>1408834</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>66,78%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>344157</t>
+          <t>344188</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>405685</t>
+          <t>404628</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>166553</t>
+          <t>178070</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>494956</t>
+          <t>495527</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>430777</t>
+          <t>448740</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>877681</t>
+          <t>874556</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,38%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>280582</t>
+          <t>281639</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>342110</t>
+          <t>342079</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>427097</t>
+          <t>426526</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>755500</t>
+          <t>743983</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>730639</t>
+          <t>733764</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1177543</t>
+          <t>1159580</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>72,1%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>522867</t>
+          <t>521182</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>583860</t>
+          <t>585332</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>663585</t>
+          <t>667022</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>780170</t>
+          <t>778286</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1204215</t>
+          <t>1209169</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1334932</t>
+          <t>1346193</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,93%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>306075</t>
+          <t>304603</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>367068</t>
+          <t>368753</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>282747</t>
+          <t>284631</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>399332</t>
+          <t>395895</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>617919</t>
+          <t>606658</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>748636</t>
+          <t>743682</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,08%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1376402</t>
+          <t>1400399</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1951046</t>
+          <t>1951534</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1585742</t>
+          <t>1587861</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2149709</t>
+          <t>2147506</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3318150</t>
+          <t>3328718</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4056925</t>
+          <t>4020537</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>57,99%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1403880</t>
+          <t>1403392</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1978524</t>
+          <t>1954527</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1429118</t>
+          <t>1431321</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1993085</t>
+          <t>1990966</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2876827</t>
+          <t>2913215</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3615602</t>
+          <t>3605034</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>51,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19C01-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91938</t>
+          <t>93150</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128897</t>
+          <t>129108</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>121995</t>
+          <t>123178</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>159403</t>
+          <t>165484</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>223956</t>
+          <t>223764</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>278838</t>
+          <t>282217</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,78%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>348940</t>
+          <t>348729</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>385899</t>
+          <t>384687</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>378701</t>
+          <t>372620</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>416109</t>
+          <t>414926</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>737103</t>
+          <t>733724</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>791985</t>
+          <t>792177</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,97%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>191647</t>
+          <t>190960</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>241109</t>
+          <t>243576</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>237997</t>
+          <t>236546</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>294580</t>
+          <t>289051</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>446828</t>
+          <t>440985</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>514448</t>
+          <t>518058</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,94%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>481019</t>
+          <t>478552</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>530481</t>
+          <t>531168</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>509646</t>
+          <t>515175</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>566229</t>
+          <t>567680</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1011906</t>
+          <t>1008296</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1079526</t>
+          <t>1085369</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>71,11%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134895</t>
+          <t>135926</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>177069</t>
+          <t>179199</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>142409</t>
+          <t>142572</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>184831</t>
+          <t>183807</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>289238</t>
+          <t>289634</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>352484</t>
+          <t>350103</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,99%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>368020</t>
+          <t>365890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>410194</t>
+          <t>409163</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>399778</t>
+          <t>400802</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>442200</t>
+          <t>442037</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>777214</t>
+          <t>779595</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>840460</t>
+          <t>840064</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,36%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>224382</t>
+          <t>222811</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>275620</t>
+          <t>270880</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>264735</t>
+          <t>267471</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>322481</t>
+          <t>321179</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>505008</t>
+          <t>507290</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>581424</t>
+          <t>578865</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>37,98%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>435571</t>
+          <t>440311</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>486809</t>
+          <t>488380</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>490586</t>
+          <t>491888</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>548332</t>
+          <t>545596</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>942835</t>
+          <t>945394</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1019251</t>
+          <t>1016969</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,72%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>687407</t>
+          <t>687219</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>777003</t>
+          <t>780082</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>813931</t>
+          <t>812786</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>907265</t>
+          <t>908419</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1525596</t>
+          <t>1521653</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1658507</t>
+          <t>1660640</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1679242</t>
+          <t>1676163</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1768838</t>
+          <t>1769026</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1832741</t>
+          <t>1831587</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1926075</t>
+          <t>1927220</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3537745</t>
+          <t>3535612</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3670656</t>
+          <t>3674599</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,72%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>113523</t>
+          <t>112024</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>153800</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>183074</t>
+          <t>184589</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>231671</t>
+          <t>231313</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>306717</t>
+          <t>307267</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>371181</t>
+          <t>373342</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>450907</t>
+          <t>452151</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>492428</t>
+          <t>493927</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>404130</t>
+          <t>404488</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>452727</t>
+          <t>451212</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>870571</t>
+          <t>868410</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>935035</t>
+          <t>934485</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,26%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>230562</t>
+          <t>229225</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>286305</t>
+          <t>288307</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>269948</t>
+          <t>270027</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>325016</t>
+          <t>328023</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>513574</t>
+          <t>517183</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>595118</t>
+          <t>597595</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,84%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>580693</t>
+          <t>578691</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>636436</t>
+          <t>637773</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>573777</t>
+          <t>570770</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>628845</t>
+          <t>628766</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1170674</t>
+          <t>1168197</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1252218</t>
+          <t>1248609</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>70,71%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>178775</t>
+          <t>179211</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>229198</t>
+          <t>228365</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>195855</t>
+          <t>196906</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>246031</t>
+          <t>247384</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>388977</t>
+          <t>387200</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>459174</t>
+          <t>459809</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,01%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>406835</t>
+          <t>407668</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>457258</t>
+          <t>456822</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>431468</t>
+          <t>430115</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>481644</t>
+          <t>480593</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>854358</t>
+          <t>853723</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>924555</t>
+          <t>926332</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,52%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>235476</t>
+          <t>239552</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>293045</t>
+          <t>293628</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>321959</t>
+          <t>321462</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>385241</t>
+          <t>381038</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>574810</t>
+          <t>573226</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>654136</t>
+          <t>656306</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,74%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>512631</t>
+          <t>512048</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>570200</t>
+          <t>566124</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>547960</t>
+          <t>552163</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>611242</t>
+          <t>611739</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1084741</t>
+          <t>1082571</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1164067</t>
+          <t>1165651</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>67,03%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>809706</t>
+          <t>805087</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>913371</t>
+          <t>907853</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1023692</t>
+          <t>1019742</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1131777</t>
+          <t>1132844</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1863103</t>
+          <t>1864483</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2017148</t>
+          <t>2018008</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,3%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2001288</t>
+          <t>2006806</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2104953</t>
+          <t>2109572</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2013518</t>
+          <t>2012451</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2121603</t>
+          <t>2125553</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4042805</t>
+          <t>4041945</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4196850</t>
+          <t>4195470</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,23%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>163651</t>
+          <t>162337</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>205085</t>
+          <t>206787</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>194306</t>
+          <t>194905</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>241899</t>
+          <t>239801</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>373189</t>
+          <t>366849</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>436954</t>
+          <t>430650</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,27%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>319908</t>
+          <t>318206</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>361342</t>
+          <t>362656</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>302464</t>
+          <t>304562</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>350057</t>
+          <t>349458</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>632402</t>
+          <t>638706</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>696167</t>
+          <t>702507</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,69%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>303922</t>
+          <t>306092</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>360603</t>
+          <t>362743</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>327808</t>
+          <t>326003</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>388669</t>
+          <t>386441</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>644144</t>
+          <t>651946</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>727692</t>
+          <t>730155</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,39%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>455743</t>
+          <t>453603</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>512424</t>
+          <t>510254</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>477704</t>
+          <t>479932</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>538565</t>
+          <t>540370</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>955027</t>
+          <t>952564</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1038575</t>
+          <t>1030773</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,26%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>190313</t>
+          <t>190956</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>239244</t>
+          <t>236845</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>224592</t>
+          <t>224837</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>272127</t>
+          <t>270970</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>428440</t>
+          <t>427691</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>495708</t>
+          <t>497236</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>44,0%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>311116</t>
+          <t>313515</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>360047</t>
+          <t>359404</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>307611</t>
+          <t>308768</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>355146</t>
+          <t>354901</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>634390</t>
+          <t>632862</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>701658</t>
+          <t>702407</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,15%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>329651</t>
+          <t>330444</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>384758</t>
+          <t>385863</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>391104</t>
+          <t>390372</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>450248</t>
+          <t>452002</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>734008</t>
+          <t>736106</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>816655</t>
+          <t>817383</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,55%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>387877</t>
+          <t>386772</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>442984</t>
+          <t>442191</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>426593</t>
+          <t>424839</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>485737</t>
+          <t>486469</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>832821</t>
+          <t>832093</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>915468</t>
+          <t>913370</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,37%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1032978</t>
+          <t>1035993</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1137089</t>
+          <t>1135352</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1193046</t>
+          <t>1186673</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1302499</t>
+          <t>1299243</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2258370</t>
+          <t>2255915</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2401253</t>
+          <t>2411091</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,59%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1527244</t>
+          <t>1528981</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1631355</t>
+          <t>1628340</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1564816</t>
+          <t>1568072</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1674269</t>
+          <t>1680642</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3130395</t>
+          <t>3120557</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3273278</t>
+          <t>3275733</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,22%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>312163</t>
+          <t>332643</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>285618</t>
+          <t>305901</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>339701</t>
+          <t>360480</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,22 +6604,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>344669</t>
+          <t>374162</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>324689</t>
+          <t>351901</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>364709</t>
+          <t>396253</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>656832</t>
+          <t>706804</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>619547</t>
+          <t>673810</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>690720</t>
+          <t>744970</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>54,55%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>299141</t>
+          <t>326888</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271603</t>
+          <t>299051</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>325686</t>
+          <t>353630</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,27 +6717,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>306863</t>
+          <t>331987</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>286823</t>
+          <t>309896</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>326843</t>
+          <t>354248</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>606004</t>
+          <t>658876</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>572116</t>
+          <t>620710</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>691870</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,66%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>651532</t>
+          <t>706149</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>651532</t>
+          <t>706149</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>651532</t>
+          <t>706149</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1262836</t>
+          <t>1365680</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1262836</t>
+          <t>1365680</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1262836</t>
+          <t>1365680</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>550276</t>
+          <t>605649</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>300437</t>
+          <t>571164</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>709114</t>
+          <t>643583</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>577991</t>
+          <t>648119</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>551884</t>
+          <t>621266</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>605751</t>
+          <t>674606</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1128267</t>
+          <t>1253768</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>700911</t>
+          <t>1211017</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1289358</t>
+          <t>1296046</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>62,77%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>617144</t>
+          <t>411482</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>458306</t>
+          <t>373548</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>866983</t>
+          <t>445967</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>364334</t>
+          <t>399665</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>336574</t>
+          <t>373178</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>390441</t>
+          <t>426518</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>981478</t>
+          <t>811147</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>820387</t>
+          <t>768869</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1408834</t>
+          <t>853898</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>41,35%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1167420</t>
+          <t>1017131</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1167420</t>
+          <t>1017131</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1167420</t>
+          <t>1017131</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2109745</t>
+          <t>2064915</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2109745</t>
+          <t>2064915</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2109745</t>
+          <t>2064915</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>374875</t>
+          <t>418344</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>344188</t>
+          <t>385317</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>404628</t>
+          <t>446952</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>373062</t>
+          <t>436331</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>178070</t>
+          <t>409457</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>495527</t>
+          <t>463521</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>747937</t>
+          <t>854675</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>448740</t>
+          <t>813162</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>874556</t>
+          <t>894555</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>57,0%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>311392</t>
+          <t>355664</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281639</t>
+          <t>327056</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>342079</t>
+          <t>388691</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>548991</t>
+          <t>359014</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>426526</t>
+          <t>331824</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>743983</t>
+          <t>385888</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>860383</t>
+          <t>714678</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>733764</t>
+          <t>674798</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1159580</t>
+          <t>756191</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>48,18%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>553896</t>
+          <t>582694</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>521182</t>
+          <t>551187</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>585332</t>
+          <t>612711</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>702120</t>
+          <t>685185</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>667022</t>
+          <t>658082</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>778286</t>
+          <t>712342</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1256015</t>
+          <t>1267879</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1209169</t>
+          <t>1223783</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1346193</t>
+          <t>1310516</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>64,74%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>336039</t>
+          <t>365265</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>304603</t>
+          <t>335248</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368753</t>
+          <t>396772</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>360797</t>
+          <t>390985</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>284631</t>
+          <t>363828</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>395895</t>
+          <t>418088</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>696836</t>
+          <t>756250</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>606658</t>
+          <t>713613</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>743682</t>
+          <t>800346</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>889935</t>
+          <t>947959</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>889935</t>
+          <t>947959</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>889935</t>
+          <t>947959</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1952851</t>
+          <t>2024129</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1952851</t>
+          <t>2024129</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1952851</t>
+          <t>2024129</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1791211</t>
+          <t>1939330</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1400399</t>
+          <t>1872035</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1951534</t>
+          <t>2002868</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1997841</t>
+          <t>2143796</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1587861</t>
+          <t>2091003</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2147506</t>
+          <t>2197801</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3789051</t>
+          <t>4083126</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3328718</t>
+          <t>3990974</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4020537</t>
+          <t>4163549</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>59,28%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1563715</t>
+          <t>1459299</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1403392</t>
+          <t>1395761</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1954527</t>
+          <t>1526594</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1580986</t>
+          <t>1481652</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1431321</t>
+          <t>1427647</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1990966</t>
+          <t>1534445</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3144701</t>
+          <t>2940951</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2913215</t>
+          <t>2860528</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3605034</t>
+          <t>3033103</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3354926</t>
+          <t>3398629</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3354926</t>
+          <t>3398629</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3354926</t>
+          <t>3398629</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6933752</t>
+          <t>7024077</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6933752</t>
+          <t>7024077</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6933752</t>
+          <t>7024077</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
